--- a/results/assessment/vIAbility/features/markers/ML/iter2/cv_results.xlsx
+++ b/results/assessment/vIAbility/features/markers/ML/iter2/cv_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -558,646 +558,560 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5103</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3468</v>
+        <v>0.1614</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2384</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3163</v>
+        <v>0.1833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2808</v>
+        <v>0.23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4749</v>
+        <v>0.4693</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0499</v>
+        <v>0.0925</v>
       </c>
       <c r="I3" t="n">
-        <v>0.106</v>
+        <v>0.1977</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0814</v>
+        <v>0.4899</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0965</v>
+        <v>0.2245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0882</v>
+        <v>0.2817</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0824</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5384</v>
+        <v>0.5103</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4204</v>
+        <v>0.3468</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4351</v>
+        <v>0.2384</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4209</v>
+        <v>0.3163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4239</v>
+        <v>0.2808</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5317</v>
+        <v>0.4749</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0741</v>
+        <v>0.0499</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0977</v>
+        <v>0.106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1633</v>
+        <v>0.0814</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1086</v>
+        <v>0.0965</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1269</v>
+        <v>0.0882</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0887</v>
+        <v>0.0824</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLPClassifier</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4928</v>
+        <v>0.5384</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2993</v>
+        <v>0.4204</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4685</v>
+        <v>0.4351</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3127</v>
+        <v>0.4209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3492</v>
+        <v>0.4239</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4907</v>
+        <v>0.5317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0471</v>
+        <v>0.0741</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1592</v>
+        <v>0.0977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3383</v>
+        <v>0.1633</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1802</v>
+        <v>0.1086</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2231</v>
+        <v>0.1269</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0366</v>
+        <v>0.0887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>MLPClassifier</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5206</v>
+        <v>0.4928</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4203</v>
+        <v>0.2993</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4779</v>
+        <v>0.4685</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4305</v>
+        <v>0.3127</v>
       </c>
       <c r="F6" t="n">
-        <v>0.447</v>
+        <v>0.3492</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4957</v>
+        <v>0.4907</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0367</v>
+        <v>0.0471</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0433</v>
+        <v>0.1592</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0563</v>
+        <v>0.3383</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0448</v>
+        <v>0.1802</v>
       </c>
       <c r="L6" t="n">
-        <v>0.048</v>
+        <v>0.2231</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0348</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TabPFN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5518</v>
+        <v>0.5206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05</v>
+        <v>0.4203</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0435</v>
+        <v>0.4779</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0485</v>
+        <v>0.4305</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0465</v>
+        <v>0.447</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5138</v>
+        <v>0.4957</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0677</v>
+        <v>0.0367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.0433</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0563</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.093</v>
+        <v>0.048</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1051</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bagging_RandomForest</t>
+          <t>TabPFN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5246</v>
+        <v>0.5518</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3274</v>
+        <v>0.05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1721</v>
+        <v>0.0435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2752</v>
+        <v>0.0485</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2238</v>
+        <v>0.0465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4656</v>
+        <v>0.5138</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0677</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1535</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1319</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1102</v>
+        <v>0.093</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bagging_SVC</t>
+          <t>Bagging_RandomForest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5414</v>
+        <v>0.5246</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.3274</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>0.1721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0916</v>
+        <v>0.2752</v>
       </c>
       <c r="F9" t="n">
-        <v>0.115</v>
+        <v>0.2238</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4775</v>
+        <v>0.4656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0723</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1614</v>
+        <v>0.1535</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1833</v>
+        <v>0.1319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.23</v>
+        <v>0.1102</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0511</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bagging_GaussianNB</t>
+          <t>Bagging_SVC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5139</v>
+        <v>0.5414</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3512</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2308</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3146</v>
+        <v>0.0916</v>
       </c>
       <c r="F10" t="n">
-        <v>0.275</v>
+        <v>0.115</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4751</v>
+        <v>0.4775</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0303</v>
+        <v>0.0723</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0382</v>
+        <v>0.1614</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0577</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0388</v>
+        <v>0.1833</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0476</v>
+        <v>0.23</v>
       </c>
       <c r="M10" t="n">
-        <v>0.053</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bagging_DecisionTree</t>
+          <t>Bagging_GaussianNB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4722</v>
+        <v>0.5139</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3069</v>
+        <v>0.3512</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2395</v>
+        <v>0.2308</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2878</v>
+        <v>0.3146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2656</v>
+        <v>0.275</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4614</v>
+        <v>0.4751</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0562</v>
+        <v>0.0303</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0701</v>
+        <v>0.0382</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0577</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0696</v>
+        <v>0.0388</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0707</v>
+        <v>0.0476</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0847</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bagging_MLPClassifier</t>
+          <t>Bagging_DecisionTree</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5938</v>
+        <v>0.4722</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.3069</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.2395</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.2878</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2656</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4614</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0067</v>
+        <v>0.0562</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.0701</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.0696</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0707</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0517</v>
+        <v>0.0847</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bagging_LogisticRegression</t>
+          <t>Bagging_MLPClassifier</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5073</v>
+        <v>0.5938</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3959</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4029</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3972</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3993</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4903</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.052</v>
+        <v>0.0067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0568</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0574</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0267</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bagging_TabPFN</t>
+          <t>Bagging_LogisticRegression</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5799</v>
+        <v>0.5073</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4067</v>
+        <v>0.3959</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0601</v>
+        <v>0.4029</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1603</v>
+        <v>0.3972</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0969</v>
+        <v>0.3993</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4872</v>
+        <v>0.4903</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0287</v>
+        <v>0.052</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3389</v>
+        <v>0.0568</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0592</v>
+        <v>0.059</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1186</v>
+        <v>0.057</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0858</v>
+        <v>0.0574</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0856</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Voting_soft_MLPClassifier+TabPFN</t>
+          <t>Bagging_TabPFN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5344</v>
+        <v>0.5799</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2349</v>
+        <v>0.4067</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1652</v>
+        <v>0.0601</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2115</v>
+        <v>0.1603</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1878</v>
+        <v>0.0969</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4912</v>
+        <v>0.4872</v>
       </c>
       <c r="H15" t="n">
-        <v>0.066</v>
+        <v>0.0287</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1993</v>
+        <v>0.3389</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1413</v>
+        <v>0.0592</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1753</v>
+        <v>0.1186</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1541</v>
+        <v>0.0858</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0851</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+SVC+DecisionTree+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5453</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.4241</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4181</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4207</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4177</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.5074</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.08550000000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1174</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1705</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.1265</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.1417</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.1054</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+SVC+DecisionTree+MLPClassifier+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5488</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4261</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3928</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.4173</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4063</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.5079</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0796</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1129</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.1527</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.1206</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.1325</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.1143</v>
+        <v>0.0856</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1608,156 +1522,6 @@
       </c>
       <c r="G15" t="n">
         <v>0.5981</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_hard_SVC+GaussianNB+DecisionTree</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3448</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.2353</v>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+SVC+GaussianNB+DecisionTree+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.4331</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.3607</v>
-      </c>
-      <c r="G17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+GaussianNB+DecisionTree+MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.5824</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.5217000000000001</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.3077</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.3871</v>
-      </c>
-      <c r="G18" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Voting_soft_MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.6385999999999999</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+SVC+DecisionTree+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.4286</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.4615</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.4348</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.4444</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.5409</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+SVC+DecisionTree+MLPClassifier+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.4945</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.5537</v>
       </c>
     </row>
   </sheetData>
